--- a/core-maths-course-tracker.xlsx
+++ b/core-maths-course-tracker.xlsx
@@ -155,7 +155,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -722,7 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -805,7 +805,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -817,7 +817,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -829,7 +829,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -841,7 +841,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -853,7 +853,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -865,7 +865,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -877,7 +877,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -901,7 +901,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -913,7 +913,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -925,7 +925,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -937,7 +937,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -949,7 +949,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -961,7 +961,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -973,7 +973,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -985,7 +985,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -997,7 +997,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -1164,6 +1164,9 @@
       <c r="G34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1193,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -1266,7 +1269,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -1277,7 +1280,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -1288,7 +1291,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1299,7 +1302,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -1310,7 +1313,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -1321,7 +1324,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -1332,7 +1335,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -1343,7 +1346,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -1354,7 +1357,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -1365,7 +1368,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1376,7 +1379,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -1387,7 +1390,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -1398,7 +1401,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -1409,7 +1412,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1420,7 +1423,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -1431,7 +1434,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -1442,7 +1445,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -1453,7 +1456,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -1464,7 +1467,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -1475,7 +1478,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -1486,7 +1489,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -1497,7 +1500,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -1508,7 +1511,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -1519,7 +1522,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -1530,7 +1533,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -1541,7 +1544,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -1552,7 +1555,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -1563,7 +1566,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -1574,7 +1577,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -1585,7 +1588,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -1595,6 +1598,9 @@
       <c r="F34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1624,7 +1630,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -1697,7 +1703,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -1708,7 +1714,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -1719,7 +1725,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1730,7 +1736,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -1741,7 +1747,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -1752,7 +1758,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -1774,7 +1780,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -1785,7 +1791,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -1796,7 +1802,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1807,7 +1813,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -1818,7 +1824,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -1829,7 +1835,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -1840,7 +1846,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1851,7 +1857,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -1862,7 +1868,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -1873,7 +1879,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -1884,7 +1890,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -1895,7 +1901,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -1906,7 +1912,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -1917,7 +1923,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -1928,7 +1934,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -1939,7 +1945,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -1950,7 +1956,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -1961,7 +1967,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -1972,7 +1978,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -1994,7 +2000,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -2005,7 +2011,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -2016,7 +2022,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -2026,6 +2032,9 @@
       <c r="F34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2056,7 +2065,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -2139,7 +2148,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -2151,7 +2160,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -2163,7 +2172,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2175,7 +2184,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -2187,7 +2196,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -2199,7 +2208,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -2211,7 +2220,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -2223,7 +2232,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -2235,7 +2244,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -2247,7 +2256,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -2259,7 +2268,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -2271,7 +2280,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -2283,7 +2292,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -2295,7 +2304,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -2307,7 +2316,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -2319,7 +2328,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -2331,7 +2340,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -2343,7 +2352,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -2355,7 +2364,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -2367,7 +2376,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -2379,7 +2388,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -2391,7 +2400,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -2403,7 +2412,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -2415,7 +2424,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -2427,7 +2436,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -2439,7 +2448,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -2451,7 +2460,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -2463,7 +2472,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -2475,7 +2484,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -2487,7 +2496,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -2498,6 +2507,9 @@
       <c r="G34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2528,7 +2540,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -2611,7 +2623,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -2623,7 +2635,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -2635,7 +2647,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2647,7 +2659,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -2659,7 +2671,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -2671,7 +2683,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -2683,7 +2695,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -2695,7 +2707,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -2707,7 +2719,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -2719,7 +2731,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -2731,7 +2743,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -2743,7 +2755,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -2755,7 +2767,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -2767,7 +2779,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -2779,7 +2791,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -2791,7 +2803,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -2803,7 +2815,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -2815,7 +2827,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -2827,7 +2839,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -2839,7 +2851,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -2851,7 +2863,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -2863,7 +2875,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -2875,7 +2887,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -2887,7 +2899,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -2899,7 +2911,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -2923,7 +2935,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -2935,7 +2947,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -2947,7 +2959,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -2959,7 +2971,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -2970,6 +2982,9 @@
       <c r="G34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2999,7 +3014,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -3072,7 +3087,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -3083,7 +3098,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -3094,7 +3109,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -3105,7 +3120,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -3116,7 +3131,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -3127,7 +3142,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -3138,7 +3153,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -3149,7 +3164,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -3160,7 +3175,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -3171,7 +3186,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -3182,7 +3197,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -3193,7 +3208,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -3204,7 +3219,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -3215,7 +3230,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -3226,7 +3241,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -3237,7 +3252,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -3248,7 +3263,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -3259,7 +3274,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -3270,7 +3285,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -3281,7 +3296,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -3292,7 +3307,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -3303,7 +3318,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -3314,7 +3329,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -3325,7 +3340,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -3336,7 +3351,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -3347,7 +3362,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -3358,7 +3373,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -3369,7 +3384,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -3380,7 +3395,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -3391,7 +3406,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -3401,6 +3416,9 @@
       <c r="F34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3429,7 +3447,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -3492,7 +3510,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -3502,7 +3520,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -3512,7 +3530,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -3522,7 +3540,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -3532,7 +3550,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -3542,7 +3560,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -3552,7 +3570,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -3562,7 +3580,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -3572,7 +3590,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -3582,7 +3600,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -3592,7 +3610,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -3602,7 +3620,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -3612,7 +3630,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -3622,7 +3640,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -3632,7 +3650,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -3642,7 +3660,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -3652,7 +3670,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -3662,7 +3680,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -3672,7 +3690,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -3682,7 +3700,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -3692,7 +3710,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -3702,7 +3720,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -3712,7 +3730,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -3722,7 +3740,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -3732,7 +3750,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -3742,7 +3760,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -3752,7 +3770,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -3762,7 +3780,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -3772,7 +3790,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -3782,7 +3800,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -3791,6 +3809,9 @@
       <c r="E34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3825,7 +3846,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -3948,7 +3969,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -3964,7 +3985,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -3980,7 +4001,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -3996,7 +4017,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -4012,7 +4033,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -4028,7 +4049,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -4044,7 +4065,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -4060,7 +4081,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -4076,7 +4097,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -4092,7 +4113,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -4108,7 +4129,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -4124,7 +4145,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -4140,7 +4161,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -4156,7 +4177,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -4172,7 +4193,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -4188,7 +4209,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -4204,7 +4225,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -4220,7 +4241,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -4236,7 +4257,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -4252,7 +4273,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -4268,7 +4289,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -4284,7 +4305,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -4300,7 +4321,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -4316,7 +4337,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -4332,7 +4353,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -4348,7 +4369,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -4364,7 +4385,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -4380,7 +4401,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -4396,7 +4417,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -4412,7 +4433,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -4427,6 +4448,9 @@
       <c r="K34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4459,7 +4483,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -4562,7 +4586,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -4576,7 +4600,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -4590,7 +4614,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -4604,7 +4628,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -4618,7 +4642,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -4632,7 +4656,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -4646,7 +4670,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -4660,7 +4684,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -4674,7 +4698,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -4688,7 +4712,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -4702,7 +4726,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -4716,7 +4740,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -4730,7 +4754,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -4744,7 +4768,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -4758,7 +4782,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -4772,7 +4796,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -4786,7 +4810,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -4800,7 +4824,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -4814,7 +4838,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -4828,7 +4852,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -4842,7 +4866,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -4856,7 +4880,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -4870,7 +4894,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -4884,7 +4908,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -4898,7 +4922,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -4912,7 +4936,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -4926,7 +4950,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -4940,7 +4964,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -4954,7 +4978,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -4968,7 +4992,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -4981,6 +5005,9 @@
       <c r="I34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5007,7 +5034,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Type each pupil's name once here. It fills in automatically on every test sheet in this workbook.</t>
@@ -5182,6 +5209,9 @@
       <c r="C34" s="13" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5212,7 +5242,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -5295,7 +5325,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -5307,7 +5337,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -5319,7 +5349,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -5331,7 +5361,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -5343,7 +5373,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -5355,7 +5385,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -5367,7 +5397,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -5379,7 +5409,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -5391,7 +5421,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -5403,7 +5433,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -5415,7 +5445,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -5427,7 +5457,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -5439,7 +5469,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -5451,7 +5481,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -5463,7 +5493,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -5475,7 +5505,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -5487,7 +5517,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -5499,7 +5529,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -5511,7 +5541,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -5523,7 +5553,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -5535,7 +5565,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -5547,7 +5577,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -5559,7 +5589,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -5571,7 +5601,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -5583,7 +5613,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -5595,7 +5625,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -5607,7 +5637,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -5619,7 +5649,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -5631,7 +5661,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -5643,7 +5673,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -5654,6 +5684,9 @@
       <c r="G34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5683,7 +5716,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -5756,7 +5789,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -5767,7 +5800,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -5778,7 +5811,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -5789,7 +5822,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -5800,7 +5833,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -5811,7 +5844,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -5822,7 +5855,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -5833,7 +5866,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -5844,7 +5877,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -5855,7 +5888,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -5866,7 +5899,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -5877,7 +5910,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -5888,7 +5921,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -5899,7 +5932,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -5910,7 +5943,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -5921,7 +5954,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -5932,7 +5965,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -5943,7 +5976,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -5954,7 +5987,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -5965,7 +5998,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -5976,7 +6009,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -5987,7 +6020,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -5998,7 +6031,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -6009,7 +6042,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -6020,7 +6053,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -6031,7 +6064,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -6042,7 +6075,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -6053,7 +6086,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -6064,7 +6097,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -6075,7 +6108,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -6085,6 +6118,9 @@
       <c r="F34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6117,7 +6153,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -6220,7 +6256,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -6234,7 +6270,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -6248,7 +6284,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -6262,7 +6298,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -6276,7 +6312,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -6290,7 +6326,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -6304,7 +6340,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -6318,7 +6354,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -6332,7 +6368,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -6346,7 +6382,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -6360,7 +6396,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -6374,7 +6410,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -6388,7 +6424,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -6402,7 +6438,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -6416,7 +6452,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -6430,7 +6466,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -6444,7 +6480,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -6458,7 +6494,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -6472,7 +6508,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -6486,7 +6522,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -6500,7 +6536,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -6514,7 +6550,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -6528,7 +6564,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -6542,7 +6578,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -6556,7 +6592,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -6570,7 +6606,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -6584,7 +6620,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -6598,7 +6634,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -6612,7 +6648,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -6626,7 +6662,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -6639,6 +6675,9 @@
       <c r="I34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6671,7 +6710,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -6774,7 +6813,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -6788,7 +6827,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -6802,7 +6841,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -6816,7 +6855,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -6830,7 +6869,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -6844,7 +6883,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -6858,7 +6897,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -6872,7 +6911,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -6886,7 +6925,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -6900,7 +6939,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -6914,7 +6953,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -6928,7 +6967,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -6942,7 +6981,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -6956,7 +6995,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -6970,7 +7009,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -6984,7 +7023,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -6998,7 +7037,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -7012,7 +7051,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -7026,7 +7065,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -7040,7 +7079,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -7054,7 +7093,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -7068,7 +7107,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -7082,7 +7121,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -7096,7 +7135,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -7110,7 +7149,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -7124,7 +7163,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -7138,7 +7177,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -7152,7 +7191,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -7166,7 +7205,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -7180,7 +7219,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -7193,6 +7232,9 @@
       <c r="I34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7224,7 +7266,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -7317,7 +7359,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -7330,7 +7372,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -7343,7 +7385,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -7356,7 +7398,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -7369,7 +7411,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -7382,7 +7424,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -7395,7 +7437,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -7408,7 +7450,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -7421,7 +7463,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -7434,7 +7476,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -7447,7 +7489,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -7460,7 +7502,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -7473,7 +7515,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -7486,7 +7528,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -7499,7 +7541,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -7512,7 +7554,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -7525,7 +7567,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -7538,7 +7580,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -7551,7 +7593,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -7564,7 +7606,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -7577,7 +7619,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -7590,7 +7632,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -7603,7 +7645,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -7616,7 +7658,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -7629,7 +7671,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -7642,7 +7684,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -7655,7 +7697,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -7668,7 +7710,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -7681,7 +7723,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -7694,7 +7736,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -7706,6 +7748,9 @@
       <c r="H34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7737,7 +7782,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -7830,7 +7875,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -7843,7 +7888,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -7856,7 +7901,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -7869,7 +7914,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -7882,7 +7927,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -7895,7 +7940,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -7908,7 +7953,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -7921,7 +7966,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -7934,7 +7979,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -7947,7 +7992,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -7960,7 +8005,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -7973,7 +8018,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -7986,7 +8031,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -7999,7 +8044,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -8012,7 +8057,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -8025,7 +8070,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -8038,7 +8083,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -8051,7 +8096,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -8064,7 +8109,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -8077,7 +8122,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -8090,7 +8135,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -8103,7 +8148,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -8116,7 +8161,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -8129,7 +8174,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -8142,7 +8187,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -8155,7 +8200,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -8168,7 +8213,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -8181,7 +8226,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -8194,7 +8239,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -8207,7 +8252,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -8219,6 +8264,9 @@
       <c r="H34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8249,7 +8297,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Enter each pupil's TOTAL mark for each question below. Leave a box blank if that pupil hasn't done this question yet.</t>
@@ -8332,7 +8380,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17">
-        <f>'Class list'!A5</f>
+        <f>IF('Class list'!A5="","",'Class list'!A5)</f>
         <v/>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -8344,7 +8392,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>'Class list'!A6</f>
+        <f>IF('Class list'!A6="","",'Class list'!A6)</f>
         <v/>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -8356,7 +8404,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17">
-        <f>'Class list'!A7</f>
+        <f>IF('Class list'!A7="","",'Class list'!A7)</f>
         <v/>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -8368,7 +8416,7 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18">
-        <f>'Class list'!A8</f>
+        <f>IF('Class list'!A8="","",'Class list'!A8)</f>
         <v/>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -8380,7 +8428,7 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17">
-        <f>'Class list'!A9</f>
+        <f>IF('Class list'!A9="","",'Class list'!A9)</f>
         <v/>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -8392,7 +8440,7 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18">
-        <f>'Class list'!A10</f>
+        <f>IF('Class list'!A10="","",'Class list'!A10)</f>
         <v/>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -8404,7 +8452,7 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17">
-        <f>'Class list'!A11</f>
+        <f>IF('Class list'!A11="","",'Class list'!A11)</f>
         <v/>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -8416,7 +8464,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="18">
-        <f>'Class list'!A12</f>
+        <f>IF('Class list'!A12="","",'Class list'!A12)</f>
         <v/>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -8428,7 +8476,7 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17">
-        <f>'Class list'!A13</f>
+        <f>IF('Class list'!A13="","",'Class list'!A13)</f>
         <v/>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -8440,7 +8488,7 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18">
-        <f>'Class list'!A14</f>
+        <f>IF('Class list'!A14="","",'Class list'!A14)</f>
         <v/>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -8452,7 +8500,7 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17">
-        <f>'Class list'!A15</f>
+        <f>IF('Class list'!A15="","",'Class list'!A15)</f>
         <v/>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -8464,7 +8512,7 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18">
-        <f>'Class list'!A16</f>
+        <f>IF('Class list'!A16="","",'Class list'!A16)</f>
         <v/>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -8476,7 +8524,7 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17">
-        <f>'Class list'!A17</f>
+        <f>IF('Class list'!A17="","",'Class list'!A17)</f>
         <v/>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -8488,7 +8536,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18">
-        <f>'Class list'!A18</f>
+        <f>IF('Class list'!A18="","",'Class list'!A18)</f>
         <v/>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -8500,7 +8548,7 @@
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17">
-        <f>'Class list'!A19</f>
+        <f>IF('Class list'!A19="","",'Class list'!A19)</f>
         <v/>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -8512,7 +8560,7 @@
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18">
-        <f>'Class list'!A20</f>
+        <f>IF('Class list'!A20="","",'Class list'!A20)</f>
         <v/>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -8524,7 +8572,7 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17">
-        <f>'Class list'!A21</f>
+        <f>IF('Class list'!A21="","",'Class list'!A21)</f>
         <v/>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -8536,7 +8584,7 @@
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18">
-        <f>'Class list'!A22</f>
+        <f>IF('Class list'!A22="","",'Class list'!A22)</f>
         <v/>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -8548,7 +8596,7 @@
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17">
-        <f>'Class list'!A23</f>
+        <f>IF('Class list'!A23="","",'Class list'!A23)</f>
         <v/>
       </c>
       <c r="B23" s="10" t="n"/>
@@ -8560,7 +8608,7 @@
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="18">
-        <f>'Class list'!A24</f>
+        <f>IF('Class list'!A24="","",'Class list'!A24)</f>
         <v/>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -8572,7 +8620,7 @@
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17">
-        <f>'Class list'!A25</f>
+        <f>IF('Class list'!A25="","",'Class list'!A25)</f>
         <v/>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -8584,7 +8632,7 @@
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="18">
-        <f>'Class list'!A26</f>
+        <f>IF('Class list'!A26="","",'Class list'!A26)</f>
         <v/>
       </c>
       <c r="B26" s="12" t="n"/>
@@ -8596,7 +8644,7 @@
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17">
-        <f>'Class list'!A27</f>
+        <f>IF('Class list'!A27="","",'Class list'!A27)</f>
         <v/>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -8608,7 +8656,7 @@
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="18">
-        <f>'Class list'!A28</f>
+        <f>IF('Class list'!A28="","",'Class list'!A28)</f>
         <v/>
       </c>
       <c r="B28" s="12" t="n"/>
@@ -8620,7 +8668,7 @@
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17">
-        <f>'Class list'!A29</f>
+        <f>IF('Class list'!A29="","",'Class list'!A29)</f>
         <v/>
       </c>
       <c r="B29" s="10" t="n"/>
@@ -8632,7 +8680,7 @@
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="18">
-        <f>'Class list'!A30</f>
+        <f>IF('Class list'!A30="","",'Class list'!A30)</f>
         <v/>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -8644,7 +8692,7 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17">
-        <f>'Class list'!A31</f>
+        <f>IF('Class list'!A31="","",'Class list'!A31)</f>
         <v/>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -8656,7 +8704,7 @@
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="18">
-        <f>'Class list'!A32</f>
+        <f>IF('Class list'!A32="","",'Class list'!A32)</f>
         <v/>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -8668,7 +8716,7 @@
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17">
-        <f>'Class list'!A33</f>
+        <f>IF('Class list'!A33="","",'Class list'!A33)</f>
         <v/>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -8680,7 +8728,7 @@
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="18">
-        <f>'Class list'!A34</f>
+        <f>IF('Class list'!A34="","",'Class list'!A34)</f>
         <v/>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -8691,6 +8739,9 @@
       <c r="G34" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>